--- a/cosmos-graph/reports/Instrument_Category_Resolution.xlsx
+++ b/cosmos-graph/reports/Instrument_Category_Resolution.xlsx
@@ -469,7 +469,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-23 19:04</t>
+          <t>Generated: 2026-09-30 18:19</t>
         </is>
       </c>
     </row>
